--- a/2022/South1/South1_members_final.xlsx
+++ b/2022/South1/South1_members_final.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>حزب البعث العربي الاشتراكي</t>
         </is>
       </c>
     </row>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>مستقل</t>
         </is>
       </c>
     </row>
